--- a/Masterdata/Technologies.xlsx
+++ b/Masterdata/Technologies.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE6A2E76-E8A2-4EC2-B37A-B6F1CB109625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E7174C-533B-4BE1-8AF4-FCABCD6F9402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Technologies" sheetId="1" r:id="rId1"/>
@@ -57,9 +62,6 @@
     <t>Machining</t>
   </si>
   <si>
-    <t>DC</t>
-  </si>
-  <si>
     <t>Die Casting</t>
   </si>
   <si>
@@ -88,13 +90,16 @@
   </si>
   <si>
     <t>Sand Casting</t>
+  </si>
+  <si>
+    <t>HPDC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +117,12 @@
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -148,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,14 +490,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -517,15 +531,15 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="3">
         <v>10000</v>
@@ -534,15 +548,15 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D4" s="3">
         <v>1000</v>
@@ -551,15 +565,15 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -568,15 +582,15 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
